--- a/data/trans_orig/P25C_R2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) en 2023</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3071</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1073,82 +1073,82 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1090</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5131</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1090</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25408</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>45348</t>
+          <t>45350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39442</t>
+          <t>39462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48883</t>
+          <t>49195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90054</t>
+          <t>90940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340161</t>
+          <t>340357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78767</t>
+          <t>79133</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85451</t>
+          <t>85618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>419007</t>
+          <t>420235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433496</t>
+          <t>433770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>772</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148946</t>
+          <t>148583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>155921</t>
+          <t>156107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>78774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84427</t>
+          <t>84917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230300</t>
+          <t>229782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>239536</t>
+          <t>239320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12756</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146947</t>
+          <t>147149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153749</t>
+          <t>153713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38573</t>
+          <t>38881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43996</t>
+          <t>44352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>188880</t>
+          <t>188164</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>196890</t>
+          <t>196808</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107087</t>
+          <t>108413</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114910</t>
+          <t>114947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>125556</t>
+          <t>124723</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>132314</t>
+          <t>132218</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39386</t>
+          <t>39568</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>825428</t>
+          <t>825958</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>844555</t>
+          <t>844082</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>317645</t>
+          <t>318278</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>329169</t>
+          <t>329494</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1147610</t>
+          <t>1147428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1173904</t>
+          <t>1173753</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C_R2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R2_2023-Edad-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>29449</t>
+          <t>32988</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24467</t>
+          <t>27553</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>58721</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>45350</t>
+          <t>54079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>661</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43885</t>
+          <t>48146</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39462</t>
+          <t>43350</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51563</t>
+          <t>55840</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49195</t>
+          <t>53134</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>95448</t>
+          <t>103985</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90940</t>
+          <t>100107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14001</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>346130</t>
+          <t>112466</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340357</t>
+          <t>108548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347127</t>
+          <t>113392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83067</t>
+          <t>87769</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79133</t>
+          <t>83272</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85618</t>
+          <t>90424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>429196</t>
+          <t>200235</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>420235</t>
+          <t>194979</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433770</t>
+          <t>203029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>347127</t>
+          <t>113392</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>347127</t>
+          <t>113392</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>347127</t>
+          <t>113392</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>92481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>92481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>92481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>434236</t>
+          <t>205873</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>434236</t>
+          <t>205873</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>434236</t>
+          <t>205873</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>153443</t>
+          <t>161520</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148583</t>
+          <t>155762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156107</t>
+          <t>164054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>82490</t>
+          <t>90278</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78774</t>
+          <t>86220</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84917</t>
+          <t>92470</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>235934</t>
+          <t>251798</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>229782</t>
+          <t>245981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>255662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>156879</t>
+          <t>165082</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>156879</t>
+          <t>165082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156879</t>
+          <t>165082</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>243078</t>
+          <t>259408</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>243078</t>
+          <t>259408</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>243078</t>
+          <t>259408</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12756</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>151250</t>
+          <t>167097</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>147149</t>
+          <t>162153</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153713</t>
+          <t>169713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>42154</t>
+          <t>45074</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>41327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>46955</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>193404</t>
+          <t>212171</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>188164</t>
+          <t>206457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>196808</t>
+          <t>215735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>155499</t>
+          <t>171602</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>155499</t>
+          <t>171602</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>155499</t>
+          <t>171602</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>48598</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>48598</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>48598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>200920</t>
+          <t>220200</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>200920</t>
+          <t>220200</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>200920</t>
+          <t>220200</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,22 +2793,22 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>504</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>112362</t>
+          <t>123861</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108413</t>
+          <t>119227</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114947</t>
+          <t>126851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17200</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>16491</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>129562</t>
+          <t>142993</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>124723</t>
+          <t>138149</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>132218</t>
+          <t>145987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>116758</t>
+          <t>128662</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>116758</t>
+          <t>128662</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116758</t>
+          <t>128662</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>134433</t>
+          <t>148297</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>134433</t>
+          <t>148297</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134433</t>
+          <t>148297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>21661</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39568</t>
+          <t>40124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>835390</t>
+          <t>645289</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>825958</t>
+          <t>636746</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>844082</t>
+          <t>650992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>324220</t>
+          <t>351359</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>318278</t>
+          <t>344510</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>329494</t>
+          <t>356698</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1159610</t>
+          <t>996648</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1147428</t>
+          <t>985985</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1173753</t>
+          <t>1004448</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
